--- a/research/traditional_assets/database/data/jordan/jordan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.1215</v>
+        <v>0.0552</v>
       </c>
       <c r="E2">
-        <v>0.04100000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="G2">
-        <v>-0.1764049125418683</v>
+        <v>0.1417995444191344</v>
       </c>
       <c r="H2">
-        <v>-0.1764049125418683</v>
+        <v>0.1417995444191344</v>
       </c>
       <c r="I2">
-        <v>0.4897655377744696</v>
+        <v>0.1205865603644647</v>
       </c>
       <c r="J2">
-        <v>0.4709423105218061</v>
+        <v>0.1110208310818835</v>
       </c>
       <c r="K2">
-        <v>-0.6589999999999999</v>
+        <v>0.802</v>
       </c>
       <c r="L2">
-        <v>-0.2452549311499814</v>
+        <v>0.1141799544419135</v>
       </c>
       <c r="M2">
-        <v>0.1</v>
+        <v>0.169</v>
       </c>
       <c r="N2">
-        <v>0.001039392994491217</v>
+        <v>0.003277734678044996</v>
       </c>
       <c r="O2">
-        <v>-0.1517450682852808</v>
+        <v>0.2107231920199501</v>
       </c>
       <c r="P2">
-        <v>0.1</v>
+        <v>0.169</v>
       </c>
       <c r="Q2">
-        <v>0.001039392994491217</v>
+        <v>0.003277734678044996</v>
       </c>
       <c r="R2">
-        <v>-0.1517450682852808</v>
+        <v>0.2107231920199501</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.063</v>
+        <v>16.217</v>
       </c>
       <c r="V2">
-        <v>0.1253819769254755</v>
+        <v>0.3145267649340573</v>
       </c>
       <c r="W2">
-        <v>-0.01234095339358497</v>
+        <v>0.02114406779661017</v>
       </c>
       <c r="X2">
-        <v>0.05374188300551208</v>
+        <v>0.1022069450363418</v>
       </c>
       <c r="Y2">
-        <v>-0.06608283639909705</v>
+        <v>-0.08106287723973167</v>
       </c>
       <c r="Z2">
-        <v>0.02110645918920405</v>
+        <v>0.12171622651972</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05370270396437202</v>
+        <v>0.1019981839071332</v>
       </c>
       <c r="AC2">
-        <v>-0.05494185623983357</v>
+        <v>-0.1019981839071332</v>
       </c>
       <c r="AD2">
-        <v>5.894</v>
+        <v>20.262</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.894</v>
+        <v>20.262</v>
       </c>
       <c r="AG2">
-        <v>-6.169</v>
+        <v>4.045000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.05772545639739873</v>
+        <v>0.2821141154520899</v>
       </c>
       <c r="AI2">
-        <v>0.04071454228951949</v>
+        <v>0.2183593413225278</v>
       </c>
       <c r="AJ2">
-        <v>-0.06851323286058573</v>
+        <v>0.07274525672151788</v>
       </c>
       <c r="AK2">
-        <v>-0.04648796919390209</v>
+        <v>0.05282402873000328</v>
       </c>
       <c r="AL2">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>3.844748858447489</v>
-      </c>
-      <c r="AO2">
-        <v>15.85542168674698</v>
+        <v>23.58789289871944</v>
       </c>
       <c r="AP2">
-        <v>-4.024135681669929</v>
-      </c>
-      <c r="AQ2">
-        <v>15.85542168674698</v>
+        <v>4.708963911525031</v>
       </c>
     </row>
     <row r="3">
@@ -722,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1568773234200743</v>
+        <v>0.5691428571428572</v>
       </c>
       <c r="H3">
-        <v>0.1568773234200743</v>
+        <v>0.5691428571428572</v>
       </c>
       <c r="I3">
-        <v>0.7472118959107806</v>
+        <v>0.484</v>
       </c>
       <c r="J3">
-        <v>0.7207119391372006</v>
+        <v>0.4644014084507042</v>
       </c>
       <c r="K3">
-        <v>1.6</v>
+        <v>0.499</v>
       </c>
       <c r="L3">
-        <v>0.5947955390334573</v>
+        <v>0.2851428571428571</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,31 +755,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.44</v>
+        <v>6</v>
       </c>
       <c r="V3">
-        <v>0.3552</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="W3">
-        <v>0.07339449541284404</v>
+        <v>0.02114406779661017</v>
       </c>
       <c r="X3">
-        <v>0.05348063665517017</v>
+        <v>0.1012497106267352</v>
       </c>
       <c r="Y3">
-        <v>0.01991385875767387</v>
+        <v>-0.08010564283012502</v>
       </c>
       <c r="Z3">
-        <v>0.1483728626585769</v>
+        <v>0.08997429305912595</v>
       </c>
       <c r="AA3">
-        <v>0.1069340935620005</v>
+        <v>0.04178418842101451</v>
       </c>
       <c r="AB3">
-        <v>0.05348063665517017</v>
+        <v>0.1012497106267352</v>
       </c>
       <c r="AC3">
-        <v>0.05345345690683034</v>
+        <v>-0.05946552220572068</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-4.44</v>
+        <v>-6</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.5508684863523574</v>
+        <v>-1.363636363636364</v>
       </c>
       <c r="AK3">
-        <v>-0.2213359920239283</v>
+        <v>-0.3157894736842105</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.208955223880598</v>
+        <v>-6.984866123399302</v>
       </c>
     </row>
     <row r="4">
@@ -841,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.12</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="E4">
-        <v>0.342</v>
+        <v>0.0368</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2.72</v>
+        <v>0.729</v>
       </c>
       <c r="L4">
-        <v>2.229508196721312</v>
+        <v>0.6394736842105263</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,31 +880,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.72</v>
+        <v>4.26</v>
       </c>
       <c r="V4">
-        <v>0.1283018867924529</v>
+        <v>0.2119402985074627</v>
       </c>
       <c r="W4">
-        <v>0.1766233766233766</v>
+        <v>0.04288235294117647</v>
       </c>
       <c r="X4">
-        <v>0.05348063665517017</v>
+        <v>0.1012497106267352</v>
       </c>
       <c r="Y4">
-        <v>0.1231427399682065</v>
+        <v>-0.05836735768555872</v>
       </c>
       <c r="Z4">
-        <v>0.09659540775930324</v>
+        <v>0.08603773584905659</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05348063665517017</v>
+        <v>0.1012497106267352</v>
       </c>
       <c r="AC4">
-        <v>-0.05348063665517017</v>
+        <v>-0.1012497106267352</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -922,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-2.72</v>
+        <v>-4.26</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -931,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1471861471861472</v>
+        <v>-0.2689393939393939</v>
       </c>
       <c r="AK4">
-        <v>-0.176853055916775</v>
+        <v>-0.3012729844413013</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al-Sanabel International for Islamic Investment (holding) (ASE:SANA)</t>
+          <t>Saba'ek Invest Company PLC (ASE:SABK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,7 +954,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.398</v>
+        <v>0.0552</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,82 +969,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.183</v>
+        <v>-0.409</v>
       </c>
       <c r="L5">
-        <v>-2.23170731707317</v>
+        <v>-0.4789227166276346</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.169</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04435695538057743</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.4132029339853301</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.169</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.04435695538057743</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0.4132029339853301</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.006</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
-        <v>0.0004511278195488722</v>
+        <v>0.6902887139107611</v>
       </c>
       <c r="W5">
-        <v>-0.008755980861244019</v>
+        <v>-0.04674285714285714</v>
       </c>
       <c r="X5">
-        <v>0.05348063665517017</v>
+        <v>0.1022069450363418</v>
       </c>
       <c r="Y5">
-        <v>-0.06223661751641418</v>
+        <v>-0.148949802179199</v>
       </c>
       <c r="Z5">
-        <v>0.003926450871480559</v>
+        <v>0.144281128569015</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05348063665517017</v>
+        <v>0.1019981839071332</v>
       </c>
       <c r="AC5">
-        <v>-0.05348063665517017</v>
+        <v>-0.1019981839071332</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="AG5">
-        <v>-0.006</v>
+        <v>-2.557</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.01879989698686583</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.008823884926870543</v>
       </c>
       <c r="AJ5">
-        <v>-0.0004513314277117497</v>
+        <v>-2.040702314445331</v>
       </c>
       <c r="AK5">
-        <v>-0.0002913469942701758</v>
+        <v>-0.4531277689172427</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rumm Financial Brokerage Co. (ASE:RUMI)</t>
+          <t>National Portfolio Securities Group (ASE:MHFZ)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,7 +1073,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0418</v>
+        <v>0.274</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1091,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-0.397</v>
+        <v>0.341</v>
       </c>
       <c r="L6">
-        <v>-1.544747081712062</v>
+        <v>0.2841666666666667</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1103,7 +1100,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1112,61 +1109,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.658</v>
+        <v>0.007</v>
       </c>
       <c r="V6">
-        <v>0.07426636568848759</v>
+        <v>0.001818181818181818</v>
       </c>
       <c r="W6">
-        <v>-0.08357894736842106</v>
+        <v>0.03666666666666667</v>
       </c>
       <c r="X6">
-        <v>0.05348063665517017</v>
+        <v>0.1062975937298625</v>
       </c>
       <c r="Y6">
-        <v>-0.1370595840235912</v>
+        <v>-0.0696309270631958</v>
       </c>
       <c r="Z6">
-        <v>0.05652078293380251</v>
+        <v>0.1470768476528986</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05348063665517017</v>
+        <v>0.1040589372790813</v>
       </c>
       <c r="AC6">
-        <v>-0.05348063665517017</v>
+        <v>-0.1040589372790813</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="AG6">
-        <v>-0.658</v>
+        <v>0.382</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.09176692616183063</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.03882623016269088</v>
       </c>
       <c r="AJ6">
-        <v>-0.08022433552792002</v>
+        <v>0.09026465028355388</v>
       </c>
       <c r="AK6">
-        <v>-0.1573409851745577</v>
+        <v>0.03815421494206952</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1183,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Portfolio Securities Group (ASE:MHFZ)</t>
+          <t>United Financial Investments Company (ASE:UCFI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1191,12 +1188,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.123</v>
-      </c>
-      <c r="E7">
-        <v>-0.26</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1210,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.12</v>
+        <v>-0.358</v>
       </c>
       <c r="L7">
-        <v>0.1857585139318885</v>
+        <v>-0.1721153846153846</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1222,7 +1213,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1231,427 +1222,67 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.6</v>
+        <v>3.32</v>
       </c>
       <c r="V7">
-        <v>0.431266846361186</v>
+        <v>0.2477611940298507</v>
       </c>
       <c r="W7">
-        <v>0.01305767138193689</v>
+        <v>-0.0328440366972477</v>
       </c>
       <c r="X7">
-        <v>0.0572793886173746</v>
+        <v>0.1750708610989356</v>
       </c>
       <c r="Y7">
-        <v>-0.04422171723543772</v>
+        <v>-0.2079148977961833</v>
       </c>
       <c r="Z7">
-        <v>0.07664926435690557</v>
+        <v>0.1903019213174749</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05640307582449696</v>
+        <v>0.1249933855756343</v>
       </c>
       <c r="AC7">
-        <v>-0.05640307582449696</v>
+        <v>-0.1249933855756343</v>
       </c>
       <c r="AD7">
-        <v>0.459</v>
+        <v>19.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.459</v>
+        <v>19.8</v>
       </c>
       <c r="AG7">
-        <v>-1.141</v>
+        <v>16.48</v>
       </c>
       <c r="AH7">
-        <v>0.110098344926841</v>
+        <v>0.5963855421686747</v>
       </c>
       <c r="AI7">
-        <v>0.04703350753150937</v>
+        <v>0.6366559485530546</v>
       </c>
       <c r="AJ7">
-        <v>-0.444141689373297</v>
+        <v>0.5515394912985274</v>
       </c>
       <c r="AK7">
-        <v>-0.1398455693099644</v>
+        <v>0.5932325413966882</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Al Bilad Securities and Investment Company (ASE:BLAD)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.172</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>-0.172</v>
-      </c>
-      <c r="L8">
-        <v>-0.2666666666666667</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0.538</v>
-      </c>
-      <c r="V8">
-        <v>0.08114630467571644</v>
-      </c>
-      <c r="W8">
-        <v>-0.01592592592592592</v>
-      </c>
-      <c r="X8">
-        <v>0.06177039105791582</v>
-      </c>
-      <c r="Y8">
-        <v>-0.07769631698384175</v>
-      </c>
-      <c r="Z8">
-        <v>0.0528775209050664</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.05912357920959577</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05912357920959577</v>
-      </c>
-      <c r="AD8">
-        <v>1.79</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>1.79</v>
-      </c>
-      <c r="AG8">
-        <v>1.252</v>
-      </c>
-      <c r="AH8">
-        <v>0.2125890736342043</v>
-      </c>
-      <c r="AI8">
-        <v>0.1410559495665878</v>
-      </c>
-      <c r="AJ8">
-        <v>0.1588429332656686</v>
-      </c>
-      <c r="AK8">
-        <v>0.1030283080974325</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>International Brokerage and Financial Markets Public Shareholding Company (ASE:IBFM)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G9">
-        <v>-0</v>
-      </c>
-      <c r="H9">
-        <v>-0</v>
-      </c>
-      <c r="I9">
-        <v>-0</v>
-      </c>
-      <c r="J9">
-        <v>-0</v>
-      </c>
-      <c r="K9">
-        <v>-3.41</v>
-      </c>
-      <c r="L9">
-        <v>0.991279069767442</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.271</v>
-      </c>
-      <c r="V9">
-        <v>0.04363929146537843</v>
-      </c>
-      <c r="W9">
-        <v>-0.3343137254901961</v>
-      </c>
-      <c r="X9">
-        <v>0.06950038065037162</v>
-      </c>
-      <c r="Y9">
-        <v>-0.4038141061405677</v>
-      </c>
-      <c r="Z9">
-        <v>-0.267122223947818</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.06468367676599239</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06468367676599239</v>
-      </c>
-      <c r="AD9">
-        <v>3.24</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>3.24</v>
-      </c>
-      <c r="AG9">
-        <v>2.969</v>
-      </c>
-      <c r="AH9">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AI9">
-        <v>0.324974924774323</v>
-      </c>
-      <c r="AJ9">
-        <v>0.3234557141300796</v>
-      </c>
-      <c r="AK9">
-        <v>0.3061140323744716</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jordan Investment Trust P.L.C (ASE:JOIT)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>-0.307</v>
-      </c>
-      <c r="G10">
-        <v>-1.526405451448041</v>
-      </c>
-      <c r="H10">
-        <v>-1.526405451448041</v>
-      </c>
-      <c r="I10">
-        <v>-1.182282793867121</v>
-      </c>
-      <c r="J10">
-        <v>-1.182282793867121</v>
-      </c>
-      <c r="K10">
-        <v>-0.9370000000000001</v>
-      </c>
-      <c r="L10">
-        <v>-1.596252129471891</v>
-      </c>
-      <c r="M10">
-        <v>0.1</v>
-      </c>
-      <c r="N10">
-        <v>0.004201680672268907</v>
-      </c>
-      <c r="O10">
-        <v>-0.1067235859124867</v>
-      </c>
-      <c r="P10">
-        <v>0.1</v>
-      </c>
-      <c r="Q10">
-        <v>0.004201680672268907</v>
-      </c>
-      <c r="R10">
-        <v>-0.1067235859124867</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>1.83</v>
-      </c>
-      <c r="V10">
-        <v>0.07689075630252101</v>
-      </c>
-      <c r="W10">
-        <v>-0.02257831325301205</v>
-      </c>
-      <c r="X10">
-        <v>0.054003129355854</v>
-      </c>
-      <c r="Y10">
-        <v>-0.07658144260886604</v>
-      </c>
-      <c r="Z10">
-        <v>0.0156067212591726</v>
-      </c>
-      <c r="AA10">
-        <v>-0.01845155801339998</v>
-      </c>
-      <c r="AB10">
-        <v>0.05392477127357388</v>
-      </c>
-      <c r="AC10">
-        <v>-0.07237632928697385</v>
-      </c>
-      <c r="AD10">
-        <v>0.405</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0.405</v>
-      </c>
-      <c r="AG10">
-        <v>-1.425</v>
-      </c>
-      <c r="AH10">
-        <v>0.0167320801487296</v>
-      </c>
-      <c r="AI10">
-        <v>0.009141180453673401</v>
-      </c>
-      <c r="AJ10">
-        <v>-0.06368715083798883</v>
-      </c>
-      <c r="AK10">
-        <v>-0.03354914655679812</v>
-      </c>
-      <c r="AL10">
-        <v>0.083</v>
-      </c>
-      <c r="AM10">
-        <v>0.083</v>
-      </c>
-      <c r="AN10">
-        <v>-0.8490566037735851</v>
-      </c>
-      <c r="AO10">
-        <v>-8.361445783132529</v>
-      </c>
-      <c r="AP10">
-        <v>2.987421383647799</v>
-      </c>
-      <c r="AQ10">
-        <v>-8.361445783132529</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,103 +588,100 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0552</v>
+        <v>0.034375</v>
       </c>
       <c r="E2">
-        <v>0.0368</v>
+        <v>-0.329</v>
       </c>
       <c r="G2">
-        <v>0.1417995444191344</v>
+        <v>-0.01873963515754561</v>
       </c>
       <c r="H2">
-        <v>0.1417995444191344</v>
+        <v>-0.01940298507462686</v>
       </c>
       <c r="I2">
-        <v>0.1205865603644647</v>
+        <v>0.07429519071310116</v>
       </c>
       <c r="J2">
-        <v>0.1110208310818835</v>
+        <v>0.06498417005879692</v>
       </c>
       <c r="K2">
-        <v>0.802</v>
+        <v>-0.346</v>
       </c>
       <c r="L2">
-        <v>0.1141799544419135</v>
+        <v>-0.05737976782752902</v>
       </c>
       <c r="M2">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.003277734678044996</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.2107231920199501</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.003277734678044996</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.2107231920199501</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>16.217</v>
+        <v>15.438</v>
       </c>
       <c r="V2">
-        <v>0.3145267649340573</v>
+        <v>0.195022738756948</v>
       </c>
       <c r="W2">
-        <v>0.02114406779661017</v>
+        <v>-0.004822110001599524</v>
       </c>
       <c r="X2">
-        <v>0.1022069450363418</v>
+        <v>0.08221334890550402</v>
       </c>
       <c r="Y2">
-        <v>-0.08106287723973167</v>
+        <v>-0.08703545890710356</v>
       </c>
       <c r="Z2">
-        <v>0.12171622651972</v>
+        <v>0.06514552408115643</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1019981839071332</v>
+        <v>0.08221240473572551</v>
       </c>
       <c r="AC2">
-        <v>-0.1019981839071332</v>
+        <v>-0.08221240473572551</v>
       </c>
       <c r="AD2">
-        <v>20.262</v>
+        <v>0.443</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20.262</v>
+        <v>0.443</v>
       </c>
       <c r="AG2">
-        <v>4.045000000000002</v>
+        <v>-14.995</v>
       </c>
       <c r="AH2">
-        <v>0.2821141154520899</v>
+        <v>0.005565116892579425</v>
       </c>
       <c r="AI2">
-        <v>0.2183593413225278</v>
+        <v>0.004045551263435705</v>
       </c>
       <c r="AJ2">
-        <v>0.07274525672151788</v>
+        <v>-0.2336943816722513</v>
       </c>
       <c r="AK2">
-        <v>0.05282402873000328</v>
+        <v>-0.1594110455536066</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>23.58789289871944</v>
+        <v>0.9651416122004357</v>
       </c>
       <c r="AP2">
-        <v>4.708963911525031</v>
+        <v>-32.66884531590414</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jordanian Expatriates Investment Holding Company (PSC) (ASE:JEIH)</t>
+          <t>Jordanian Expatriates Investment Holding Company (ASE:JEIH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,23 +712,29 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.116</v>
+      </c>
+      <c r="E3">
+        <v>-0.329</v>
+      </c>
       <c r="G3">
-        <v>0.5691428571428572</v>
+        <v>-0.07647058823529412</v>
       </c>
       <c r="H3">
-        <v>0.5691428571428572</v>
+        <v>-0.07647058823529412</v>
       </c>
       <c r="I3">
-        <v>0.484</v>
+        <v>0.2928104575163399</v>
       </c>
       <c r="J3">
-        <v>0.4644014084507042</v>
+        <v>0.2190374331550802</v>
       </c>
       <c r="K3">
-        <v>0.499</v>
+        <v>0.309</v>
       </c>
       <c r="L3">
-        <v>0.2851428571428571</v>
+        <v>0.2019607843137255</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="V3">
-        <v>0.5769230769230769</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="W3">
-        <v>0.02114406779661017</v>
+        <v>0.01282157676348548</v>
       </c>
       <c r="X3">
-        <v>0.1012497106267352</v>
+        <v>0.08209541822208943</v>
       </c>
       <c r="Y3">
-        <v>-0.08010564283012502</v>
+        <v>-0.06927384145860396</v>
       </c>
       <c r="Z3">
-        <v>0.08997429305912595</v>
+        <v>0.08453038674033149</v>
       </c>
       <c r="AA3">
-        <v>0.04178418842101451</v>
+        <v>0.01851531893520844</v>
       </c>
       <c r="AB3">
-        <v>0.1012497106267352</v>
+        <v>0.08209541822208943</v>
       </c>
       <c r="AC3">
-        <v>-0.05946552220572068</v>
+        <v>-0.06358009928688099</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-6</v>
+        <v>-7.5</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.363636363636364</v>
+        <v>-1.923076923076923</v>
       </c>
       <c r="AK3">
-        <v>-0.3157894736842105</v>
+        <v>-0.4213483146067415</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-6.984866123399302</v>
+        <v>-16.33986928104575</v>
       </c>
     </row>
     <row r="4">
@@ -835,10 +838,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.08740000000000001</v>
-      </c>
-      <c r="E4">
-        <v>0.0368</v>
+        <v>-0.00745</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.729</v>
+        <v>0.058</v>
       </c>
       <c r="L4">
-        <v>0.6394736842105263</v>
+        <v>0.04393939393939394</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,31 +880,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.26</v>
+        <v>3.52</v>
       </c>
       <c r="V4">
-        <v>0.2119402985074627</v>
+        <v>0.1768844221105528</v>
       </c>
       <c r="W4">
-        <v>0.04288235294117647</v>
+        <v>0.003152173913043479</v>
       </c>
       <c r="X4">
-        <v>0.1012497106267352</v>
+        <v>0.08209541822208943</v>
       </c>
       <c r="Y4">
-        <v>-0.05836735768555872</v>
+        <v>-0.07894324430904595</v>
       </c>
       <c r="Z4">
-        <v>0.08603773584905659</v>
+        <v>0.09335219236209337</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1012497106267352</v>
+        <v>0.08209541822208943</v>
       </c>
       <c r="AC4">
-        <v>-0.1012497106267352</v>
+        <v>-0.08209541822208943</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-4.26</v>
+        <v>-3.52</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -925,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.2689393939393939</v>
+        <v>-0.2148962148962149</v>
       </c>
       <c r="AK4">
-        <v>-0.3012729844413013</v>
+        <v>-0.2349799732977303</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saba'ek Invest Company PLC (ASE:SABK)</t>
+          <t>Rumm Financial Brokerage (ASE:RUMI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0552</v>
+        <v>0.297</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.003603603603603603</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -969,85 +969,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.409</v>
+        <v>-0.19</v>
       </c>
       <c r="L5">
-        <v>-0.4789227166276346</v>
+        <v>-0.1711711711711712</v>
       </c>
       <c r="M5">
-        <v>0.169</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04435695538057743</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0.4132029339853301</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.169</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.04435695538057743</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0.4132029339853301</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>0.6902887139107611</v>
+        <v>0.3651315789473685</v>
       </c>
       <c r="W5">
-        <v>-0.04674285714285714</v>
+        <v>-0.03653846153846154</v>
       </c>
       <c r="X5">
-        <v>0.1022069450363418</v>
+        <v>0.08209541822208943</v>
       </c>
       <c r="Y5">
-        <v>-0.148949802179199</v>
+        <v>-0.118633879760551</v>
       </c>
       <c r="Z5">
-        <v>0.144281128569015</v>
+        <v>0.2913385826771653</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1019981839071332</v>
+        <v>0.08209541822208943</v>
       </c>
       <c r="AC5">
-        <v>-0.1019981839071332</v>
+        <v>-0.08209541822208943</v>
       </c>
       <c r="AD5">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-2.557</v>
+        <v>-1.11</v>
       </c>
       <c r="AH5">
-        <v>0.01879989698686583</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.008823884926870543</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-2.040702314445331</v>
+        <v>-0.5751295336787565</v>
       </c>
       <c r="AK5">
-        <v>-0.4531277689172427</v>
+        <v>-0.2846153846153847</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Portfolio Securities Group (ASE:MHFZ)</t>
+          <t>Jordan Investment Trust P.L.C (ASE:JOIT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1073,7 +1070,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.274</v>
+        <v>-0.138</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1088,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.341</v>
+        <v>-0.318</v>
       </c>
       <c r="L6">
-        <v>0.2841666666666667</v>
+        <v>-0.4356164383561644</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1100,7 +1097,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1109,61 +1106,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.007</v>
+        <v>0.211</v>
       </c>
       <c r="V6">
-        <v>0.001818181818181818</v>
+        <v>0.005656836461126006</v>
       </c>
       <c r="W6">
-        <v>0.03666666666666667</v>
+        <v>-0.007775061124694377</v>
       </c>
       <c r="X6">
-        <v>0.1062975937298625</v>
+        <v>0.08233127958891863</v>
       </c>
       <c r="Y6">
-        <v>-0.0696309270631958</v>
+        <v>-0.09010634071361301</v>
       </c>
       <c r="Z6">
-        <v>0.1470768476528986</v>
+        <v>0.01786719533984385</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1040589372790813</v>
+        <v>0.08232939124936159</v>
       </c>
       <c r="AC6">
-        <v>-0.1040589372790813</v>
+        <v>-0.08232939124936159</v>
       </c>
       <c r="AD6">
-        <v>0.389</v>
+        <v>0.254</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.389</v>
+        <v>0.254</v>
       </c>
       <c r="AG6">
-        <v>0.382</v>
+        <v>0.04300000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.09176692616183063</v>
+        <v>0.006763593758321352</v>
       </c>
       <c r="AI6">
-        <v>0.03882623016269088</v>
+        <v>0.005913302602784374</v>
       </c>
       <c r="AJ6">
-        <v>0.09026465028355388</v>
+        <v>0.001151487561256461</v>
       </c>
       <c r="AK6">
-        <v>0.03815421494206952</v>
+        <v>0.001006012680438902</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1180,7 +1177,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Financial Investments Company (ASE:UCFI)</t>
+          <t>Saba'ek Invest Company PLC (ASE:SABK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1188,6 +1185,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.0762</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-0.358</v>
+        <v>-0.187</v>
       </c>
       <c r="L7">
-        <v>-0.1721153846153846</v>
+        <v>-0.3169491525423729</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1228,60 +1228,176 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3.32</v>
+        <v>2.34</v>
       </c>
       <c r="V7">
-        <v>0.2477611940298507</v>
+        <v>0.6446280991735537</v>
       </c>
       <c r="W7">
-        <v>-0.0328440366972477</v>
+        <v>-0.02280487804878049</v>
       </c>
       <c r="X7">
-        <v>0.1750708610989356</v>
+        <v>0.08245800244080886</v>
       </c>
       <c r="Y7">
-        <v>-0.2079148977961833</v>
+        <v>-0.1052628804895894</v>
       </c>
       <c r="Z7">
-        <v>0.1903019213174749</v>
+        <v>0.1045543150806309</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1249933855756343</v>
+        <v>0.0824537972186835</v>
       </c>
       <c r="AC7">
-        <v>-0.1249933855756343</v>
+        <v>-0.0824537972186835</v>
       </c>
       <c r="AD7">
-        <v>19.8</v>
+        <v>0.038</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>19.8</v>
+        <v>0.038</v>
       </c>
       <c r="AG7">
-        <v>16.48</v>
+        <v>-2.302</v>
       </c>
       <c r="AH7">
-        <v>0.5963855421686747</v>
+        <v>0.01035986913849509</v>
       </c>
       <c r="AI7">
-        <v>0.6366559485530546</v>
+        <v>0.004751187796949237</v>
       </c>
       <c r="AJ7">
-        <v>0.5515394912985274</v>
+        <v>-1.733433734939759</v>
       </c>
       <c r="AK7">
-        <v>0.5932325413966882</v>
+        <v>-0.406857546836338</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>National Portfolio Securities Group (ASE:MHFZ)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.15</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-0.018</v>
+      </c>
+      <c r="L8">
+        <v>-0.024</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.757</v>
+      </c>
+      <c r="V8">
+        <v>0.1946015424164524</v>
+      </c>
+      <c r="W8">
+        <v>-0.001869158878504673</v>
+      </c>
+      <c r="X8">
+        <v>0.08343991347176255</v>
+      </c>
+      <c r="Y8">
+        <v>-0.08530907235026722</v>
+      </c>
+      <c r="Z8">
+        <v>0.07491010787055533</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.0833880546075956</v>
+      </c>
+      <c r="AC8">
+        <v>-0.0833880546075956</v>
+      </c>
+      <c r="AD8">
+        <v>0.151</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.151</v>
+      </c>
+      <c r="AG8">
+        <v>-0.606</v>
+      </c>
+      <c r="AH8">
+        <v>0.03736698836921554</v>
+      </c>
+      <c r="AI8">
+        <v>0.0155014885535366</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.184531059683313</v>
+      </c>
+      <c r="AK8">
+        <v>-0.06745325022261799</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
